--- a/result/train_info_resnet18_part_detrend_plr_stft_bin_win_lcc.xlsx
+++ b/result/train_info_resnet18_part_detrend_plr_stft_bin_win_lcc.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5294248712806787</v>
+        <v>0.5243374129859689</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4111825810557992</v>
+        <v>0.3938566608541816</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8078781122259383</v>
+        <v>0.8299888517279822</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9118811881188119</v>
+        <v>0.7968697968697969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6827279466271312</v>
+        <v>0.8869532987398072</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7808393387028402</v>
+        <v>0.8395018417821435</v>
       </c>
       <c r="I2" t="n">
-        <v>56.27315521240234</v>
+        <v>36.19093799591064</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3173736426896273</v>
+        <v>0.335625998277278</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3061469781416408</v>
+        <v>0.2796868089388108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8777406168710516</v>
+        <v>0.8842437755481234</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9497354497354498</v>
+        <v>0.8672566371681416</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7983691623424759</v>
+        <v>0.9080800593031876</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8674989931534434</v>
+        <v>0.8871989860583016</v>
       </c>
       <c r="I3" t="n">
-        <v>56.00608348846436</v>
+        <v>36.05696940422058</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1981891932084957</v>
+        <v>0.2331273956348868</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1739759241952699</v>
+        <v>0.1809951541118721</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9340393905611297</v>
+        <v>0.9292084726867336</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9057845514374784</v>
+        <v>0.9559228650137741</v>
       </c>
       <c r="G4" t="n">
-        <v>0.969236471460341</v>
+        <v>0.9002965159377316</v>
       </c>
       <c r="H4" t="n">
-        <v>0.936436884512086</v>
+        <v>0.9272761977476618</v>
       </c>
       <c r="I4" t="n">
-        <v>56.14226102828979</v>
+        <v>35.94746398925781</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1324106206934772</v>
+        <v>0.1648814572633021</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1368814272029028</v>
+        <v>0.1269970193213216</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9459308807134894</v>
+        <v>0.9511334076551468</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9492347891004106</v>
+        <v>0.9641631719405261</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9425500370644923</v>
+        <v>0.9373610081541883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9458806025664869</v>
+        <v>0.9505732005262169</v>
       </c>
       <c r="I5" t="n">
-        <v>56.3744330406189</v>
+        <v>35.84103226661682</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1035396678312329</v>
+        <v>0.1169771640215562</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1000076866482754</v>
+        <v>0.09061491576480794</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9635823114083983</v>
+        <v>0.9656261612783352</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9539187227866474</v>
+        <v>0.9790316431566908</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9744255003706449</v>
+        <v>0.9518161601186064</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9640630729739641</v>
+        <v>0.9652320992294682</v>
       </c>
       <c r="I6" t="n">
-        <v>56.58672881126404</v>
+        <v>36.17112803459167</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07943684036565328</v>
+        <v>0.08819106752869367</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09608650341431593</v>
+        <v>0.0973173071735004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.966183574879227</v>
+        <v>0.9643255295429208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9648928307464892</v>
+        <v>0.9440113394755493</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9677538917716827</v>
+        <v>0.9873980726464048</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9663212435233161</v>
+        <v>0.9652173913043478</v>
       </c>
       <c r="I7" t="n">
-        <v>56.96172142028809</v>
+        <v>36.04670476913452</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05819811534228559</v>
+        <v>0.07116269929916424</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1054418295196164</v>
+        <v>0.07696638487488824</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9589371980676329</v>
+        <v>0.9736157562244518</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9538292414803957</v>
+        <v>0.9772218073188947</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9647887323943662</v>
+        <v>0.9699777613046702</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9592776856458448</v>
+        <v>0.9735863095238095</v>
       </c>
       <c r="I8" t="n">
-        <v>57.32848167419434</v>
+        <v>36.03565883636475</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05680297460146858</v>
+        <v>0.05961138617166389</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06699469071790884</v>
+        <v>0.07279093798901611</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9778892604979561</v>
+        <v>0.9747305834262356</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9677185346391005</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9888806523350631</v>
+        <v>0.9651593773165308</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9781851512373969</v>
+        <v>0.9745508982035929</v>
       </c>
       <c r="I9" t="n">
-        <v>57.20074200630188</v>
+        <v>36.01931858062744</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.04530124144436982</v>
+        <v>0.05312489448713739</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08283910746121305</v>
+        <v>0.08396682113453129</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9749163879598662</v>
+        <v>0.9689706428836864</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9588256355173649</v>
+        <v>0.9910748932867676</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9466271312083024</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9754143143325441</v>
+        <v>0.9683412322274881</v>
       </c>
       <c r="I10" t="n">
-        <v>57.37387013435364</v>
+        <v>36.01535105705261</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04053200756436294</v>
+        <v>0.04101493620522317</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04547144236048607</v>
+        <v>0.1100325799924625</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9836492010405053</v>
+        <v>0.9659977703455964</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9840504451038575</v>
+        <v>0.9834678969627066</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9833209785025945</v>
+        <v>0.9481097108969607</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9836855765665554</v>
+        <v>0.965465182109832</v>
       </c>
       <c r="I11" t="n">
-        <v>58.1365749835968</v>
+        <v>37.4154942035675</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03547817709180077</v>
+        <v>0.03932769392058495</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1480735718612229</v>
+        <v>0.03986533428507873</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9572649572649573</v>
+        <v>0.9869936826458565</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9916334661354582</v>
+        <v>0.9855875831485588</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9225352112676056</v>
+        <v>0.9885100074128984</v>
       </c>
       <c r="H12" t="n">
-        <v>0.955837173579109</v>
+        <v>0.9870466321243523</v>
       </c>
       <c r="I12" t="n">
-        <v>58.34890747070312</v>
+        <v>41.02069664001465</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03657362534647965</v>
+        <v>0.03475479582130195</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04620737576142185</v>
+        <v>0.05991534249424472</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9827201783723523</v>
+        <v>0.9801189149015236</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9872802095024317</v>
+        <v>0.981419546636938</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9781319495922906</v>
+        <v>0.9788732394366197</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9826847886799479</v>
+        <v>0.9801447392837261</v>
       </c>
       <c r="I13" t="n">
-        <v>58.76972246170044</v>
+        <v>40.94982314109802</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02916540368260111</v>
+        <v>0.03459239732756045</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.069560456132384</v>
+        <v>0.05197763606043499</v>
       </c>
       <c r="E14" t="n">
-        <v>0.976960237829803</v>
+        <v>0.9830917874396136</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9791511541325391</v>
+        <v>0.9804644305197199</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9747961452928094</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9769687964338781</v>
+        <v>0.9831824062095731</v>
       </c>
       <c r="I14" t="n">
-        <v>58.94230818748474</v>
+        <v>40.88047695159912</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03010332451731099</v>
+        <v>0.03220186959836652</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07560471249138109</v>
+        <v>0.07397947448564793</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9710144927536232</v>
+        <v>0.9732441471571907</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9735469448584203</v>
+        <v>0.9907763259031515</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9684951816160119</v>
+        <v>0.955522609340252</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9710144927536232</v>
+        <v>0.9728301886792453</v>
       </c>
       <c r="I15" t="n">
-        <v>59.74026989936829</v>
+        <v>40.85809779167175</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02535528608843533</v>
+        <v>0.0253993128445617</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.05025230173125571</v>
+        <v>0.05100690508426647</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9834633965068748</v>
+        <v>0.9819769602378298</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9844040103973264</v>
+        <v>0.9775982372383401</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9825796886582654</v>
+        <v>0.9866567828020756</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9834910035243926</v>
+        <v>0.9821066223943922</v>
       </c>
       <c r="I16" t="n">
-        <v>60.56045913696289</v>
+        <v>40.50813245773315</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02130508144044272</v>
+        <v>0.0252032770518081</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04400179826326602</v>
+        <v>0.05930148918297384</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9860646599777034</v>
+        <v>0.9786324786324786</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9798755945847054</v>
+        <v>0.9950172479877347</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9621942179392142</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9861903885104032</v>
+        <v>0.9783305068777087</v>
       </c>
       <c r="I17" t="n">
-        <v>61.5944344997406</v>
+        <v>40.77037048339844</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02192387980260464</v>
+        <v>0.02214799685703435</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03807751085821363</v>
+        <v>0.04961618019947121</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9873652917131178</v>
+        <v>0.9829059829059829</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9892113095238095</v>
+        <v>0.9765910753474762</v>
       </c>
       <c r="G18" t="n">
-        <v>0.985544848035582</v>
+        <v>0.9896219421793921</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9873746750835499</v>
+        <v>0.9830633284241531</v>
       </c>
       <c r="I18" t="n">
-        <v>60.36194849014282</v>
+        <v>40.82306408882141</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01619710223486675</v>
+        <v>0.0209567401840269</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.04657518275580406</v>
+        <v>0.042566029984903</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9879227053140096</v>
+        <v>0.9860646599777034</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9827649431609827</v>
+        <v>0.9958412098298677</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9762787249814677</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9880184331797235</v>
+        <v>0.9859629421673217</v>
       </c>
       <c r="I19" t="n">
-        <v>60.18898844718933</v>
+        <v>40.70230722427368</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0226233933062488</v>
+        <v>0.01964332665011711</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04308132828780196</v>
+        <v>0.03493168662116551</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9881085098476403</v>
+        <v>0.9873652917131178</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9856194690265486</v>
+        <v>0.987759643916914</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9907338769458859</v>
+        <v>0.9870274277242401</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9881700554528651</v>
+        <v>0.9873934000741564</v>
       </c>
       <c r="I20" t="n">
-        <v>59.50211882591248</v>
+        <v>40.83961987495422</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01708660977305852</v>
+        <v>0.01970591801740438</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.04119779442481079</v>
+        <v>0.05512430648455127</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9882943143812709</v>
+        <v>0.9821627647714605</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9841969864020581</v>
+        <v>0.9931766489764974</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9710896960711638</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9883742387894445</v>
+        <v>0.9820089955022488</v>
       </c>
       <c r="I21" t="n">
-        <v>59.43590664863586</v>
+        <v>40.41327047348022</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01691435285230145</v>
+        <v>0.01820034620879764</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04170205761678</v>
+        <v>0.03617002510485658</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9871794871794872</v>
+        <v>0.9881085098476403</v>
       </c>
       <c r="F22" t="n">
-        <v>0.990302126072361</v>
+        <v>0.9885014836795252</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9840622683469237</v>
+        <v>0.9877687175685693</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9871723368655884</v>
+        <v>0.9881349647756766</v>
       </c>
       <c r="I22" t="n">
-        <v>59.87739539146423</v>
+        <v>40.89488434791565</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01401351225843226</v>
+        <v>0.01445683485871996</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03827230407465139</v>
+        <v>0.02442273940489257</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9868078781122259</v>
+        <v>0.9916387959866221</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9870226177233964</v>
+        <v>0.9911144020733061</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9866567828020756</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9868396663577387</v>
+        <v>0.9916651231709576</v>
       </c>
       <c r="I23" t="n">
-        <v>59.17829942703247</v>
+        <v>40.87773084640503</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01724747032621666</v>
+        <v>0.01379389401026342</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03588777467722629</v>
+        <v>0.03750760962826009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9895949461166852</v>
+        <v>0.9869936826458565</v>
       </c>
       <c r="F24" t="n">
-        <v>0.987094395280236</v>
+        <v>0.9873887240356083</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.9866567828020756</v>
       </c>
       <c r="H24" t="n">
-        <v>0.989648798521257</v>
+        <v>0.9870226177233964</v>
       </c>
       <c r="I24" t="n">
-        <v>59.15435338020325</v>
+        <v>40.42408108711243</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01432690711044686</v>
+        <v>0.01677809659070808</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02985445719745117</v>
+        <v>0.03054554600161142</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9908955778520996</v>
+        <v>0.989223337049424</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9882049391817177</v>
+        <v>0.9870848708487084</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9909443725743855</v>
+        <v>0.9892751479289941</v>
       </c>
       <c r="I25" t="n">
-        <v>58.5030791759491</v>
+        <v>40.89830255508423</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01177515326297533</v>
+        <v>0.0151429593019902</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04452130635948879</v>
+        <v>0.0264592366527281</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9851356373095503</v>
+        <v>0.9903381642512077</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9844559585492227</v>
+        <v>0.9929210134128167</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9859154929577465</v>
+        <v>0.9877687175685693</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9851851851851852</v>
+        <v>0.9903381642512077</v>
       </c>
       <c r="I26" t="n">
-        <v>58.33104205131531</v>
+        <v>40.78265643119812</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01426845420611145</v>
+        <v>0.0119011736225154</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.03254081300052435</v>
+        <v>0.04418545250781569</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9899665551839465</v>
+        <v>0.9845782237086584</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9929157345264727</v>
+        <v>0.9906191369606003</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9870274277242401</v>
+        <v>0.9785025945144552</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9899628252788104</v>
+        <v>0.9845235875442849</v>
       </c>
       <c r="I27" t="n">
-        <v>57.61130571365356</v>
+        <v>40.80337071418762</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01108918926876833</v>
+        <v>0.01203894606675713</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03167473266904171</v>
+        <v>0.03295186922795325</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9901523597175771</v>
+        <v>0.9886659234485321</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9925512104283054</v>
+        <v>0.9842085934630922</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H28" t="n">
-        <v>0.990154189113877</v>
+        <v>0.9887474635676075</v>
       </c>
       <c r="I28" t="n">
-        <v>57.76073217391968</v>
+        <v>40.77701711654663</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.009923837088647438</v>
+        <v>0.01161327785480441</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02681187334671594</v>
+        <v>0.03020641971646877</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9912671869193609</v>
+        <v>0.990709773318469</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9864220183486239</v>
+        <v>0.9951383694839192</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.986286137879911</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9913332104001475</v>
+        <v>0.990692479523455</v>
       </c>
       <c r="I29" t="n">
-        <v>57.6411600112915</v>
+        <v>40.85303592681885</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.009686134775490568</v>
+        <v>0.01349316729285763</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0328856071295775</v>
+        <v>0.03348332108205085</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9914529914529915</v>
+        <v>0.989223337049424</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9885777450257922</v>
+        <v>0.9874446085672083</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9911045218680504</v>
       </c>
       <c r="H30" t="n">
-        <v>0.99150036954915</v>
+        <v>0.9892711801701812</v>
       </c>
       <c r="I30" t="n">
-        <v>57.38452363014221</v>
+        <v>40.57401371002197</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01392577272719472</v>
+        <v>0.009168467926729014</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05231666711321618</v>
+        <v>0.02429397195787204</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9838350055741361</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9946949602122016</v>
+        <v>0.9925816023738873</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9729429206819866</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H31" t="n">
-        <v>0.983698707138842</v>
+        <v>0.9922135706340378</v>
       </c>
       <c r="I31" t="n">
-        <v>57.2989342212677</v>
+        <v>40.59165239334106</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.006556407275144162</v>
+        <v>0.01012726893465601</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02319244581101443</v>
+        <v>0.03064186560476031</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9929394277220365</v>
+        <v>0.9905239687848384</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9896907216494846</v>
+        <v>0.9896411394746578</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9929811599556705</v>
+        <v>0.9905573042029254</v>
       </c>
       <c r="I32" t="n">
-        <v>57.91407704353333</v>
+        <v>40.59175896644592</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.009879958989103706</v>
+        <v>0.009634644639625368</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03457386515271359</v>
+        <v>0.02876809591401786</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9905239687848384</v>
+        <v>0.9903381642512077</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9849761817515573</v>
+        <v>0.9889135254988913</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9906025428413489</v>
+        <v>0.9903774981495189</v>
       </c>
       <c r="I33" t="n">
-        <v>57.09011292457581</v>
+        <v>40.67159223556519</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.008294289444110363</v>
+        <v>0.008850806923859323</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02980965769325074</v>
+        <v>0.02503868097142945</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9908955778520996</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9871276204486944</v>
+        <v>0.9925760950259837</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9911045218680504</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9909544028059811</v>
+        <v>0.9918397626112759</v>
       </c>
       <c r="I34" t="n">
-        <v>57.0824453830719</v>
+        <v>40.53799533843994</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.006524205701346534</v>
+        <v>0.008602253346729288</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03646531194525235</v>
+        <v>0.02866359640872022</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9901523597175771</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9903596588802372</v>
+        <v>0.9936638091688409</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9881393624907339</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9901760889712697</v>
+        <v>0.9908938858948151</v>
       </c>
       <c r="I35" t="n">
-        <v>56.82150769233704</v>
+        <v>40.19083595275879</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01067415221146576</v>
+        <v>0.006329759002173306</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.02258798070078868</v>
+        <v>0.02019164585371497</v>
       </c>
       <c r="E36" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9933110367892977</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9929472902746845</v>
+        <v>0.9955323901712584</v>
       </c>
       <c r="G36" t="n">
-        <v>0.991475166790215</v>
+        <v>0.9911045218680504</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9922106824925816</v>
+        <v>0.9933135215453195</v>
       </c>
       <c r="I36" t="n">
-        <v>57.011887550354</v>
+        <v>39.99754357337952</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.006413301194520142</v>
+        <v>0.00625058298550476</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02667072473389469</v>
+        <v>0.01638785587544304</v>
       </c>
       <c r="E37" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9889543446244478</v>
+        <v>0.9966430436404327</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9922423346878463</v>
+        <v>0.99349321435211</v>
       </c>
       <c r="I37" t="n">
-        <v>56.95743942260742</v>
+        <v>39.92665886878967</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.006432963592166836</v>
+        <v>0.00881463495429664</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.02833087429402192</v>
+        <v>0.03587589038590371</v>
       </c>
       <c r="E38" t="n">
-        <v>0.989223337049424</v>
+        <v>0.9884801189149015</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9852941176470589</v>
+        <v>0.9977341389728097</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9792438843587843</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9892949427833149</v>
+        <v>0.9884025439580996</v>
       </c>
       <c r="I38" t="n">
-        <v>57.19443273544312</v>
+        <v>39.962162733078</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.00735467351513293</v>
+        <v>0.005712434078732515</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.02087038219275663</v>
+        <v>0.0290384069675055</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9940542549238202</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F39" t="n">
-        <v>0.991519174041298</v>
+        <v>0.9958893871449925</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9877687175685693</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9940850277264325</v>
+        <v>0.9918124302195758</v>
       </c>
       <c r="I39" t="n">
-        <v>56.79956746101379</v>
+        <v>40.15301585197449</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.005076533596438024</v>
+        <v>0.005528994182932474</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.02099714635615788</v>
+        <v>0.02643715665499527</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9934968413229283</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9911471781630394</v>
+        <v>0.9936708860759493</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9892512972572276</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9935293030134961</v>
+        <v>0.9914561664190193</v>
       </c>
       <c r="I40" t="n">
-        <v>56.54438018798828</v>
+        <v>40.54128408432007</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.004484327337887201</v>
+        <v>0.006225540700255871</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02690683393663175</v>
+        <v>0.03218239824707662</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9923820141211446</v>
+        <v>0.9903381642512077</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9878810135879544</v>
+        <v>0.9981174698795181</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9825796886582654</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9924368197749492</v>
+        <v>0.9902876354127755</v>
       </c>
       <c r="I41" t="n">
-        <v>56.52024531364441</v>
+        <v>40.03368735313416</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.006222304133755265</v>
+        <v>0.003871769336492542</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.02833537746977871</v>
+        <v>0.02636520833628784</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9905239687848384</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9896411394746578</v>
+        <v>0.9940630797773655</v>
       </c>
       <c r="G42" t="n">
-        <v>0.991475166790215</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9905573042029254</v>
+        <v>0.9935101056925645</v>
       </c>
       <c r="I42" t="n">
-        <v>56.5370397567749</v>
+        <v>40.08667278289795</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.007529974960348436</v>
+        <v>0.005409819067482943</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.03212987368583015</v>
+        <v>0.02041847477507415</v>
       </c>
       <c r="E43" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9932935916542474</v>
+        <v>0.9977595220313666</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9881393624907339</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H43" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9940476190476191</v>
       </c>
       <c r="I43" t="n">
-        <v>56.64858984947205</v>
+        <v>39.91493511199951</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.00388416468567298</v>
+        <v>0.001480101324958866</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.04797017931667454</v>
+        <v>0.03240754495128337</v>
       </c>
       <c r="E44" t="n">
-        <v>0.986250464511334</v>
+        <v>0.9905239687848384</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9733044733044733</v>
+        <v>0.9878363435311464</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H44" t="n">
-        <v>0.986471663619744</v>
+        <v>0.9905747551284421</v>
       </c>
       <c r="I44" t="n">
-        <v>56.72391295433044</v>
+        <v>39.81256747245789</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.004690268110284591</v>
+        <v>0.007306996285609903</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.04574883217816485</v>
+        <v>0.02273267821236209</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9875510962467484</v>
+        <v>0.9927536231884058</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9928812289246909</v>
+        <v>0.9973812196034418</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9822090437361009</v>
+        <v>0.9881393624907339</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9875163033351966</v>
+        <v>0.9927387823496555</v>
       </c>
       <c r="I45" t="n">
-        <v>56.79024863243103</v>
+        <v>39.63299536705017</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.00451426621408586</v>
+        <v>0.005642250658051474</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.03241625780898585</v>
+        <v>0.05514299636172853</v>
       </c>
       <c r="E46" t="n">
-        <v>0.992196209587514</v>
+        <v>0.9810479375696767</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9911242603550295</v>
+        <v>0.9988470407378939</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.963306152705708</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9922251018141429</v>
+        <v>0.980754716981132</v>
       </c>
       <c r="I46" t="n">
-        <v>56.72845888137817</v>
+        <v>39.27967476844788</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.003964588186836124</v>
+        <v>0.003223274318850634</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03595096362467426</v>
+        <v>0.01859699647453055</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9910813823857302</v>
+        <v>0.9942400594574508</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9885693215339233</v>
+        <v>0.9933407325194229</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9911275415896488</v>
+        <v>0.9942603221625624</v>
       </c>
       <c r="I47" t="n">
-        <v>56.69410824775696</v>
+        <v>39.52714681625366</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.002945906085188251</v>
+        <v>0.003818954024125102</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.03579909555307263</v>
+        <v>0.02210142918233376</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9901523597175771</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9878273699741793</v>
+        <v>0.9966392830470501</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9892512972572276</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9902015159918655</v>
+        <v>0.9929315476190477</v>
       </c>
       <c r="I48" t="n">
-        <v>57.12684464454651</v>
+        <v>39.57696461677551</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.003984554473298849</v>
+        <v>0.005664636999019427</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0287479681101911</v>
+        <v>0.02997696738096093</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9920104050538833</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9915129151291513</v>
+        <v>0.9911209766925638</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9937130177514792</v>
+        <v>0.9920385113867802</v>
       </c>
       <c r="I49" t="n">
-        <v>56.68786573410034</v>
+        <v>39.65582942962646</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.004283804406790387</v>
+        <v>0.002799652058142357</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.02880207762580045</v>
+        <v>0.01671232737026433</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9916387959866221</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9922077922077922</v>
+        <v>0.9962880475129918</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9911045218680504</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9916558501761543</v>
+        <v>0.9955489614243324</v>
       </c>
       <c r="I50" t="n">
-        <v>56.81744480133057</v>
+        <v>40.15252804756165</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.002289115766904411</v>
+        <v>0.002684600720924491</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.02825461755719381</v>
+        <v>0.0293321160820045</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.9920104050538833</v>
       </c>
       <c r="F51" t="n">
-        <v>0.994060876020787</v>
+        <v>0.9878721058434399</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9925871015567087</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9933234421364985</v>
+        <v>0.9920649566340654</v>
       </c>
       <c r="I51" t="n">
-        <v>56.60214352607727</v>
+        <v>40.7813618183136</v>
       </c>
     </row>
   </sheetData>
